--- a/Trắc nghiệm bài kiểm tra đánh giá đầu vào/danhgianangluc/da-dwh-easy.xlsx
+++ b/Trắc nghiệm bài kiểm tra đánh giá đầu vào/danhgianangluc/da-dwh-easy.xlsx
@@ -460,19 +460,19 @@
         <v>Fact Table chứa các dữ liệu số đo lường được (metrics/measures like revenue, quantity) và các khóa ngoại liên kết với các bảng chiều (Dimension Tables).</v>
       </c>
       <c r="F2" t="str">
+        <v>Mã nguồn các câu lệnh SQL dùng để tạo lập cấu trúc database của hệ thống — mã nguồn kỹ thuật</v>
+      </c>
+      <c r="G2" t="str">
         <v>Các số liệu đo lường định lượng và khóa ngoại trỏ tới các bảng chiều — số liệu đo lường và khóa liên kết</v>
       </c>
-      <c r="G2" t="str">
+      <c r="H2" t="str">
+        <v>Danh sách phân quyền đăng nhập của các nhân viên vận hành kho hàng — phân quyền nhân sự</v>
+      </c>
+      <c r="I2" t="str">
         <v>Các thuộc tính văn bản mô tả bối cảnh của đối tượng như tên, địa chỉ khách hàng — thuộc tính mô tả</v>
       </c>
-      <c r="H2" t="str">
-        <v>Mã nguồn các câu lệnh SQL dùng để tạo lập cấu trúc database của hệ thống — mã nguồn kỹ thuật</v>
-      </c>
-      <c r="I2" t="str">
-        <v>Danh sách phân quyền đăng nhập của các nhân viên vận hành kho hàng — phân quyền nhân sự</v>
-      </c>
       <c r="J2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -492,19 +492,19 @@
         <v>Dimension Table chứa các thuộc tính mô tả (như thông tin khách hàng, sản phẩm, địa lý, thời gian) dùng để lọc, phân nhóm (group by) và phân tích dữ liệu trong Fact Table.</v>
       </c>
       <c r="F3" t="str">
-        <v>Cung cấp thông tin bối cảnh chi tiết (Ai, Cái gì, Ở đâu, Khi nào) để giải nghĩa cho dữ liệu trong Fact Table — cung cấp bối cảnh phân tích</v>
+        <v>Lưu trữ tổng số tiền giao dịch lũy kế của toàn bộ hệ thống bán hàng — lưu trữ số tiền tổng</v>
       </c>
       <c r="G3" t="str">
-        <v>Lưu trữ tổng số tiền giao dịch lũy kế của toàn bộ hệ thống bán hàng — lưu trữ số tiền tổng</v>
+        <v>Tự động xóa các bản ghi dữ liệu trùng lặp khi người dùng gửi yêu cầu — dọn dẹp dữ liệu</v>
       </c>
       <c r="H3" t="str">
         <v>Mã hóa toàn bộ các bản ghi dữ liệu trước khi nạp vào hệ thống để bảo mật — mã hóa dữ liệu</v>
       </c>
       <c r="I3" t="str">
-        <v>Tự động xóa các bản ghi dữ liệu trùng lặp khi người dùng gửi yêu cầu — dọn dẹp dữ liệu</v>
+        <v>Cung cấp thông tin bối cảnh chi tiết (Ai, Cái gì, Ở đâu, Khi nào) để giải nghĩa cho dữ liệu trong Fact Table — cung cấp bối cảnh phân tích</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -524,19 +524,19 @@
         <v>ETL là quy trình tích hợp dữ liệu cơ bản: Trích xuất dữ liệu từ các nguồn (Extract), Biến đổi dữ liệu cho sạch và đúng chuẩn (Transform), rồi Nạp vào kho dữ liệu (Load).</v>
       </c>
       <c r="F4" t="str">
+        <v>Estimation - Testing - Launch — Ước lượng, Kiểm thử, Ra mắt sản phẩm phần mềm — quy trình dự án</v>
+      </c>
+      <c r="G4" t="str">
+        <v>Entity - Table - Logic — Thực thể, Bảng dữ liệu, Logic nghiệp vụ hệ thống — cấu trúc database</v>
+      </c>
+      <c r="H4" t="str">
         <v>Extract - Transform - Load — Trích xuất, Biến đổi, Nạp dữ liệu vào kho dữ liệu — quy trình nạp dữ liệu</v>
       </c>
-      <c r="G4" t="str">
+      <c r="I4" t="str">
         <v>Enterprise - Target - License — Doanh nghiệp, Mục tiêu, Bản quyền phần mềm — quy trình doanh nghiệp</v>
       </c>
-      <c r="H4" t="str">
-        <v>Entity - Table - Logic — Thực thể, Bảng dữ liệu, Logic nghiệp vụ hệ thống — cấu trúc database</v>
-      </c>
-      <c r="I4" t="str">
-        <v>Estimation - Testing - Launch — Ước lượng, Kiểm thử, Ra mắt sản phẩm phần mềm — quy trình dự án</v>
-      </c>
       <c r="J4">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -556,19 +556,19 @@
         <v>Star Schema là mô hình đơn giản và phổ biến nhất trong DWH: 1 Fact Table ở giữa liên kết trực tiếp với các Dimension Tables qua mối quan hệ 1-n, trông giống hình ngôi sao.</v>
       </c>
       <c r="F5" t="str">
+        <v>Các bảng dữ liệu được xếp tuần tự thành một hàng dọc từ trên xuống dưới — mô hình tuyến tính</v>
+      </c>
+      <c r="G5" t="str">
         <v>Một Fact Table nằm ở trung tâm và kết nối trực tiếp với các Dimension Tables xung quanh — mô hình hình sao trực tiếp</v>
       </c>
-      <c r="G5" t="str">
+      <c r="H5" t="str">
+        <v>Toàn bộ dữ liệu của hệ thống được gộp chung vào đúng 1 bảng lớn duy nhất — mô hình phẳng</v>
+      </c>
+      <c r="I5" t="str">
         <v>Nhiều Fact Tables kết nối chéo với nhau mà không cần các Dimension Tables — mô hình Fact liên kết</v>
       </c>
-      <c r="H5" t="str">
-        <v>Các bảng dữ liệu được xếp tuần tự thành một hàng dọc từ trên xuống dưới — mô hình tuyến tính</v>
-      </c>
-      <c r="I5" t="str">
-        <v>Toàn bộ dữ liệu của hệ thống được gộp chung vào đúng 1 bảng lớn duy nhất — mô hình phẳng</v>
-      </c>
       <c r="J5">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -588,19 +588,19 @@
         <v>OLTP (Online Transaction Processing) tối ưu hóa cho ghi/đọc nhanh các giao dịch đơn lẻ (như tạo đơn hàng). OLAP (Online Analytical Processing) tối ưu hóa cho truy vấn tổng hợp phức tạp trên lượng dữ liệu lớn để làm báo cáo.</v>
       </c>
       <c r="F6" t="str">
-        <v>OLTP dùng cho các giao dịch hàng ngày thời gian thực; OLAP dùng cho phân tích dữ liệu và báo cáo — giao dịch nhanh vs phân tích sâu</v>
+        <v>OLTP do khách hàng tự quản lý; còn OLAP do nhà nước quản lý bảo mật — chủ thể quản trị hệ thống</v>
       </c>
       <c r="G6" t="str">
         <v>OLTP chỉ lưu trữ được hình ảnh; còn OLAP chỉ lưu trữ được các con số — loại hình dữ liệu lưu trữ</v>
       </c>
       <c r="H6" t="str">
+        <v>OLTP dùng cho các giao dịch hàng ngày thời gian thực; OLAP dùng cho phân tích dữ liệu và báo cáo — giao dịch nhanh vs phân tích sâu</v>
+      </c>
+      <c r="I6" t="str">
         <v>OLTP chạy trên điện thoại di động; còn OLAP chỉ chạy được trên máy tính mainframe — môi trường phần cứng chạy</v>
       </c>
-      <c r="I6" t="str">
-        <v>OLTP do khách hàng tự quản lý; còn OLAP do nhà nước quản lý bảo mật — chủ thể quản trị hệ thống</v>
-      </c>
       <c r="J6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -620,19 +620,19 @@
         <v>Data Mart là một kho dữ liệu con, được thiết kế chuyên biệt cho nhu cầu sử dụng của một phòng ban hoặc một nhóm người dùng cụ thể trong doanh nghiệp.</v>
       </c>
       <c r="F7" t="str">
+        <v>Bảng danh sách toàn bộ các sản phẩm bị lỗi và phải trả lại nhà sản xuất — danh sách lỗi sản phẩm</v>
+      </c>
+      <c r="G7" t="str">
+        <v>Phần mềm dùng để tự động quét virus cho máy chủ cơ sở dữ liệu của dự án — diệt virus</v>
+      </c>
+      <c r="H7" t="str">
         <v>Một phân vùng kho dữ liệu thu nhỏ, tập trung vào một chủ đề hoặc một bộ phận cụ thể (như Tài chính, Sales) — kho dữ liệu chuyên biệt</v>
       </c>
-      <c r="G7" t="str">
+      <c r="I7" t="str">
         <v>Một siêu thị trực tuyến bán các bộ dữ liệu mẫu cho các nhà nghiên cứu khoa học — chợ bán dữ liệu</v>
       </c>
-      <c r="H7" t="str">
-        <v>Phần mềm dùng để tự động quét virus cho máy chủ cơ sở dữ liệu của dự án — diệt virus</v>
-      </c>
-      <c r="I7" t="str">
-        <v>Bảng danh sách toàn bộ các sản phẩm bị lỗi và phải trả lại nhà sản xuất — danh sách lỗi sản phẩm</v>
-      </c>
       <c r="J7">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -658,10 +658,10 @@
         <v>Chỉ duy nhất cơ sở dữ liệu Microsoft SQL Server — giới hạn nguồn dữ liệu</v>
       </c>
       <c r="H8" t="str">
+        <v>Bản vẽ thiết kế Figma của giao diện trang quản trị quản lý kho — bản vẽ UI</v>
+      </c>
+      <c r="I8" t="str">
         <v>Chỉ các file ảnh PNG/JPG chụp từ camera giám sát — nguồn dữ liệu hình ảnh</v>
-      </c>
-      <c r="I8" t="str">
-        <v>Bản vẽ thiết kế Figma của giao diện trang quản trị quản lý kho — bản vẽ UI</v>
       </c>
       <c r="J8">
         <v>1</v>
@@ -687,13 +687,13 @@
         <v>Quản lý và lưu trữ thông tin lịch sử khi các thuộc tính trong bảng chiều thay đổi theo thời gian — theo dõi biến động lịch sử</v>
       </c>
       <c r="G9" t="str">
+        <v>Tự động nén dung lượng của các bảng dữ liệu cũ đã lưu trên 5 năm — nén dữ liệu cũ</v>
+      </c>
+      <c r="H9" t="str">
+        <v>Đồng bộ hóa dữ liệu mật khẩu của người dùng khi họ đổi thông tin đăng nhập — đồng bộ mật khẩu</v>
+      </c>
+      <c r="I9" t="str">
         <v>Tăng tốc độ ghi dữ liệu của Fact Table lên nhanh gấp 10 lần — tăng tốc độ ghi dữ liệu</v>
-      </c>
-      <c r="H9" t="str">
-        <v>Tự động nén dung lượng của các bảng dữ liệu cũ đã lưu trên 5 năm — nén dữ liệu cũ</v>
-      </c>
-      <c r="I9" t="str">
-        <v>Đồng bộ hóa dữ liệu mật khẩu của người dùng khi họ đổi thông tin đăng nhập — đồng bộ mật khẩu</v>
       </c>
       <c r="J9">
         <v>1</v>
@@ -716,19 +716,19 @@
         <v>Trong Snowflake Schema, các Dimension Tables được chuẩn hóa để loại bỏ trùng lặp dữ liệu (phân rã thành các bảng con, ví dụ: Product -&gt; Subcategory -&gt; Category), làm sơ đồ trông giống hình bông tuyết.</v>
       </c>
       <c r="F10" t="str">
+        <v>Bông tuyết không sử dụng Fact Table mà chỉ sử dụng duy nhất các bảng chiều — không có bảng sự kiện</v>
+      </c>
+      <c r="G10" t="str">
         <v>Các bảng chiều trong Snowflake được chuẩn hóa (normalized) và phân rã thành nhiều bảng chiều con liên kết với nhau — bảng chiều chuẩn hóa</v>
       </c>
-      <c r="G10" t="str">
+      <c r="H10" t="str">
+        <v>Bông tuyết chỉ hỗ trợ lưu trữ dữ liệu thời tiết và nhiệt độ môi trường — giới hạn loại dữ liệu</v>
+      </c>
+      <c r="I10" t="str">
         <v>Bông tuyết bắt buộc phải sử dụng các máy chủ đặt tại các nước có khí hậu lạnh giá — vị trí địa lý chạy máy chủ</v>
       </c>
-      <c r="H10" t="str">
-        <v>Bông tuyết không sử dụng Fact Table mà chỉ sử dụng duy nhất các bảng chiều — không có bảng sự kiện</v>
-      </c>
-      <c r="I10" t="str">
-        <v>Bông tuyết chỉ hỗ trợ lưu trữ dữ liệu thời tiết và nhiệt độ môi trường — giới hạn loại dữ liệu</v>
-      </c>
       <c r="J10">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -748,19 +748,19 @@
         <v>Transform là giai đoạn biến đổi dữ liệu thô (raw data) thu được từ nguồn thành dữ liệu sạch, có cấu trúc nhất quán để sẵn sàng nạp vào kho.</v>
       </c>
       <c r="F11" t="str">
+        <v>Xóa bỏ toàn bộ các bảng chiều và chỉ giữ lại duy nhất một bảng sự kiện — dọn dẹp cấu trúc bảng</v>
+      </c>
+      <c r="G11" t="str">
         <v>Làm sạch dữ liệu, chuẩn hóa định dạng, lọc bản ghi lỗi, mã hóa và tổng hợp dữ liệu — xử lý định dạng dữ liệu</v>
       </c>
-      <c r="G11" t="str">
+      <c r="H11" t="str">
         <v>Gửi email thông báo báo cáo doanh số hàng ngày cho ban giám đốc công ty — gửi email báo cáo</v>
-      </c>
-      <c r="H11" t="str">
-        <v>Xóa bỏ toàn bộ các bảng chiều và chỉ giữ lại duy nhất một bảng sự kiện — dọn dẹp cấu trúc bảng</v>
       </c>
       <c r="I11" t="str">
         <v>Viết mã nguồn Javascript để thiết kế hiệu ứng trượt cho trang web bán hàng — hiệu ứng giao diện</v>
       </c>
       <c r="J11">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
